--- a/교재/엑셀교재v2/019_데이터베이스함수_실습.xlsx
+++ b/교재/엑셀교재v2/019_데이터베이스함수_실습.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FORYOUCOM\Documents\CompUse2nd\교재\엑셀교재v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC92AEDE-E5BD-45A3-84E3-E1862EEE729A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C54E245-8369-4CC9-878E-99D229EEBFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36495" yWindow="3675" windowWidth="16380" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="실습" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,24 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">추가정답!$B$17:$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="57">
   <si>
     <t>데이터베이스 함수 실습</t>
   </si>
@@ -215,16 +228,22 @@
     <font>
       <sz val="11"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -740,9 +759,7 @@
         <v>50</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
     </row>
@@ -1034,9 +1051,7 @@
     </row>
     <row r="26" spans="1:10" ht="27.95" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>

--- a/교재/엑셀교재v2/019_데이터베이스함수_실습.xlsx
+++ b/교재/엑셀교재v2/019_데이터베이스함수_실습.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -331,6 +331,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -941,10 +944,12 @@
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
     </row>
-    <row r="18" spans="1:10" ht="27.95" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
-        <v>33</v>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액 합계 (DSUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -955,10 +960,12 @@
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
     </row>
-    <row r="19" spans="1:10" ht="27.95" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="11" t="s">
-        <v>34</v>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점 판매수량 최대값 (DMAX 함수 사용)</t>
+        </is>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -969,10 +976,12 @@
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="27.95" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
-        <v>35</v>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에어컨 판매금액 최소값 (DMIN 함수 사용)</t>
+        </is>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -983,10 +992,12 @@
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="27.95" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
-        <v>36</v>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강남점 판매수량 평균 (DAVERAGE 함수 사용)</t>
+        </is>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -997,10 +1008,12 @@
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="27.95" customHeight="1">
+    <row r="22" spans="1:10" ht="44" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="11" t="s">
-        <v>37</v>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액의 숫자 개수 (DCOUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -1011,10 +1024,12 @@
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
     </row>
-    <row r="23" spans="1:10" ht="27.95" customHeight="1">
+    <row r="23" spans="1:10" ht="44" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="11" t="s">
-        <v>38</v>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점 대리점의 비어 있지 않은 개수 (DCOUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -1542,10 +1557,12 @@
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
     </row>
-    <row r="18" spans="1:10" ht="27.95" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
-        <v>33</v>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액 합계 (DSUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -1559,10 +1576,12 @@
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
     </row>
-    <row r="19" spans="1:10" ht="27.95" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="11" t="s">
-        <v>34</v>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점 판매수량 최대값 (DMAX 함수 사용)</t>
+        </is>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -1576,10 +1595,12 @@
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="27.95" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
-        <v>35</v>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에어컨 판매금액 최소값 (DMIN 함수 사용)</t>
+        </is>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -1593,10 +1614,12 @@
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="27.95" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
-        <v>36</v>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강남점 판매수량 평균 (DAVERAGE 함수 사용)</t>
+        </is>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -1610,10 +1633,12 @@
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="27.95" customHeight="1">
+    <row r="22" spans="1:10" ht="44" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="11" t="s">
-        <v>37</v>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액의 숫자 개수 (DCOUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -1627,10 +1652,12 @@
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
     </row>
-    <row r="23" spans="1:10" ht="27.95" customHeight="1">
+    <row r="23" spans="1:10" ht="44" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="11" t="s">
-        <v>38</v>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서초점 대리점의 비어 있지 않은 개수 (DCOUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -2021,10 +2048,12 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="27.95" customHeight="1">
+    <row r="17" spans="1:10" ht="44" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
-        <v>49</v>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액에서 숫자 개수 (DCOUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -2035,10 +2064,12 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27.95" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
-        <v>50</v>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액에서 비어 있지 않은 개수 (DCOUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -2049,10 +2080,12 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27.95" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="11" t="s">
-        <v>51</v>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 번호에서 비어 있지 않은 개수 (DCOUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -2063,10 +2096,12 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="27.95" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
-        <v>52</v>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV이면서 판매금액 100 이상 합계 (DSUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -2077,10 +2112,12 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="27.95" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
-        <v>53</v>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 또는 에어컨 판매금액 합계 (DSUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -2491,10 +2528,12 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="27.95" customHeight="1">
+    <row r="17" spans="1:10" ht="44" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
-        <v>49</v>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액에서 숫자 개수 (DCOUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -2508,10 +2547,12 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27.95" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
-        <v>50</v>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 판매금액에서 비어 있지 않은 개수 (DCOUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -2525,10 +2566,12 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27.95" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="11" t="s">
-        <v>51</v>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 번호에서 비어 있지 않은 개수 (DCOUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -2542,10 +2585,12 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="27.95" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
-        <v>52</v>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV이면서 판매금액 100 이상 합계 (DSUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -2559,10 +2604,12 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="27.95" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
-        <v>53</v>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV 또는 에어컨 판매금액 합계 (DSUM 함수 사용)</t>
+        </is>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
